--- a/results/job_matches_2026-05-13.xlsx
+++ b/results/job_matches_2026-05-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b20e14df8f336ad</t>
+          <t>https://www.indeed.com/viewjob?jk=aec208cdfd014f62</t>
         </is>
       </c>
     </row>
@@ -543,20 +543,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=569e2680cf991081</t>
+          <t>https://www.indeed.com/viewjob?jk=f4b12692ab49b7bf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Optum Advisory Board - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, S3, Azure, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff403bb7c12a386</t>
+          <t>https://www.indeed.com/viewjob?jk=569e2680cf991081</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer – Baltimore City, MD</t>
+          <t>Data Engineer - Optum Advisory Board - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ac3e71ab2ea33f</t>
+          <t>https://www.indeed.com/viewjob?jk=dff403bb7c12a386</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software (API)Engineer- Dallas, TX</t>
+          <t>Data Engineer – Baltimore City, MD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Oracle, DynamoDB</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f42bf20e03caa36</t>
+          <t>https://www.indeed.com/viewjob?jk=80ac3e71ab2ea33f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software (API)Engineer- Dallas, TX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Benchmark Solutions LLC</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Oracle, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8cfebbb7e871628</t>
+          <t>https://www.indeed.com/viewjob?jk=8f42bf20e03caa36</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, UDS Data Management - East</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad1f7dab55752b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=f200c5b28338d187</t>
         </is>
       </c>
     </row>
@@ -853,60 +853,60 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer - Java</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Step Functions, S3, SQS, SNS, RDS, Databricks</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b239490817bb3dba</t>
+          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>DevOps Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Creative Realities</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d8317116e3b8b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer - Java</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>POWERX</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
+          <t>https://www.indeed.com/viewjob?jk=78d222e67b861731</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Specialist</t>
+          <t>Data Engineer, Machine Learning, Manufacturing Quality</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Creative Realities</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Kafka, Oracle, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
+          <t>https://www.indeed.com/viewjob?jk=ae09bf0f698805e7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>POWERX</t>
+          <t>Encore Fire Protection</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Needham, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d222e67b861731</t>
+          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, BigQuery, Spark, Snowflake</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d24c78be0131037</t>
+          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Encore Fire Protection</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=8348059168d7d3ed</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fuse Fundraising</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8348059168d7d3ed</t>
+          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Development Infostructure</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, API Gateway, RDS, Azure, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e5739e46621f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer- Dallas, TX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fuse Fundraising</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
+          <t>https://www.indeed.com/viewjob?jk=440518c253bc8566</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Dallas, TX</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=440518c253bc8566</t>
+          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Databricks Data Engineer(Strong Testing Experience)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Quadrant Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ae1d7b6ce452d8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer(Strong Testing Experience)</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Quadrant Technologies</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ae1d7b6ce452d8</t>
+          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>St. Jude Children's Research Hospital</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,77 +1711,77 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>Assurant</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Azure Data Fabric Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>SLD TECHNOLOGIES LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8429c2a459d3de4f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Sr. Software Engineer, Popeyes</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ifm efector inc.</t>
+          <t>Popeyes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Azure Data Fabric Engineer</t>
+          <t>Senior Data Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SLD TECHNOLOGIES LLC</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud &amp; Database Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>enChoice, Inc.</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Cloud Storage, Scala, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7de1e2049e683c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software/Data Engineer</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>ifm efector inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
+          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Cloud &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Paradigm Max Q LLC</t>
+          <t>enChoice, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Cloud Storage, Scala, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7de1e2049e683c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Popeyes</t>
+          <t>Senior Software/Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Popeyes</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer- Dallas, TX</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Paradigm Max Q LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84593a6570df58c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Developer (Java Full Stack)</t>
+          <t>Senior Quality Engineer- Dallas, TX</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
+          <t>https://www.indeed.com/viewjob?jk=84593a6570df58c9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr. Software QA Engineer, Logistics</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
+          <t>https://www.indeed.com/viewjob?jk=3703a65a658398ce</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Developer (Java Full Stack)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, HBase, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=930af228e501f878</t>
+          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Senior Data Engineer _ Python with Spark</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Myrtle Point, OR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b780cbd54e20e82</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8b463a5152c979</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer _ Python with Spark</t>
+          <t>Associate, Snowflake Data Engineer – BTO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8b463a5152c979</t>
+          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=256f30d9aec8fc7b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, HBase, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c70bbdfbf97a8c</t>
+          <t>https://www.indeed.com/viewjob?jk=930af228e501f878</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770392</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6a7bc10ac96c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=256f30d9aec8fc7b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770393</t>
+          <t>Software Engineer, MLOps, Manufacturing Quality</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c054ad41fdd40c</t>
+          <t>https://www.indeed.com/viewjob?jk=552f3d2b25f75144</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Backend ML Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Sterling Computers</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>North Sioux City, SD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0c294f11382975</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Backend ML Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Sterling Computers</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8e8eb0ff879575</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - UnderwritingCenter</t>
+          <t>Backend Software Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4f413a4cd84f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c70bbdfbf97a8c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sales/Solutions Engineer</t>
+          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770392</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Artie</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c1fe1287b79994</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6a7bc10ac96c1a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770393</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Main Sail, LLC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake</t>
+          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5675e83788c1c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=23c054ad41fdd40c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,42 +2551,42 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57c71c270f4f024f</t>
+          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
+          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RXO</t>
+          <t>Main Sail, LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eedaefa82474ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=5675e83788c1c4fd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Performance Test Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Rhino</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
+          <t>AWS, S3, ECS, RDS, Scala, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
+          <t>https://www.indeed.com/viewjob?jk=42875591a11e5caa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Privacy &amp; Governance</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pacers Sports &amp; Entertainment</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Data Modeling, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b85de9f1c3e87c3</t>
+          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
+          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Urban Dynamics</t>
+          <t>RXO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
+          <t>https://www.indeed.com/viewjob?jk=eedaefa82474ae57</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Performance Test Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
+          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer (Python, Kafka / Confluent)</t>
+          <t>Senior Data Engineer - Privacy &amp; Governance</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Data Modeling, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
+          <t>https://www.indeed.com/viewjob?jk=4b85de9f1c3e87c3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Sr. Database Administrator</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Meridian Cooperative Inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
+          <t>https://www.indeed.com/viewjob?jk=aad5be160ea34501</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Sr. Data Architect, Large Scale Distributed Systems</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL, AKS, Git, SQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
+          <t>https://www.indeed.com/viewjob?jk=ab772be531586550</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Urban Dynamics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
+          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
+          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Manufacturing Systems Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>voestalpine</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
+          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Software Engineer (Python, Kafka / Confluent)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
+          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
+          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
+          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
+          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
+          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
+          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
+          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
+          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Synctera</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
+          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer II - Identity &amp; Access Management</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc0ef7396ea02ef</t>
+          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL, dbt, Git</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Financial Data Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>cpg.io eCommerce Distributors</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Addison, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
+          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,84 +3716,84 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
+          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d09fe840e33b4c7</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
+          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3803,15 +3803,15 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
+          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Synctera</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
+          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Software Engineer II - Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc0ef7396ea02ef</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL, dbt, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior Data Engineer - Informatica IDMC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior Financial Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>cpg.io eCommerce Distributors</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Addison, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
+          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
+          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
+          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
+          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
+          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
+          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
+          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f93ad8b1a8de327</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, SQL Server, ETL, Git, Python, SQL, R</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7bca3fc6f7be967</t>
+          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Python Engineer with REST &amp; GenAI</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
+          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer — ChainIT Pay</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ChainIT Pay</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
+          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
+          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Vidoori</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hyattsville, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7710e703cc72f4b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, PySpark, Scala, Power BI, Git, Python, SQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9af17a3ab15e53</t>
+          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
+          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Pelago</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,15 +4721,260 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f93ad8b1a8de327</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Python Engineer with REST &amp; GenAI</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer — ChainIT Pay</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ChainIT Pay</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Guild Mortgage Company LLC</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Business Intelligence SME – MicroStrategy</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>A1fed</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Pelago</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, MySQL, NoSQL</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a095b7520f3a9612</t>
         </is>

--- a/results/job_matches_2026-05-13.xlsx
+++ b/results/job_matches_2026-05-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software (API)Engineer- Dallas, TX</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Oracle, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f42bf20e03caa36</t>
+          <t>https://www.indeed.com/viewjob?jk=f200c5b28338d187</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f200c5b28338d187</t>
+          <t>https://www.indeed.com/viewjob?jk=919dcee2ea81fef5</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=919dcee2ea81fef5</t>
+          <t>https://www.indeed.com/viewjob?jk=a4076bfbb84ccf37</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>#19675 - Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Qualitest</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4076bfbb84ccf37</t>
+          <t>https://www.indeed.com/viewjob?jk=83236b2299aaa9b3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>#19675 - Data Engineer</t>
+          <t>Software Engineer - Java</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83236b2299aaa9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - Java</t>
+          <t>DevOps Specialist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Creative Realities</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Specialist</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Creative Realities</t>
+          <t>POWERX</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
+          <t>https://www.indeed.com/viewjob?jk=78d222e67b861731</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>POWERX</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,89 +951,89 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d222e67b861731</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer, Machine Learning, Manufacturing Quality</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Fuse Fundraising</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Kafka, Oracle, MySQL, MongoDB</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae09bf0f698805e7</t>
+          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Encore Fire Protection</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Needham, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, MySQL, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9585bb14bb3c50d</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Sr Databricks Data Engineer(Strong Testing Experience)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Quadrant Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,46 +1042,46 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4350b7356581efc</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ae1d7b6ce452d8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=110879d3c05b187b</t>
+          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
         </is>
       </c>
     </row>
@@ -1103,20 +1103,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa4c8179a8ac4da</t>
+          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66f1fbb6c8a1a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc984a42640329e</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ifm efector inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfdcd1adce614e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data Fabric Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>SLD TECHNOLOGIES LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3763e7b5c9b674</t>
+          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>enChoice, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Cloud Storage, Scala, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb6a218ca916697</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7de1e2049e683c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software/Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d791e762f6d81f87</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Paradigm Max Q LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7943d064127358c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e64b70ed3febe9</t>
+          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8348059168d7d3ed</t>
+          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Assurant</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer, Popeyes</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fuse Fundraising</t>
+          <t>Popeyes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
+          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Developer (Java Full Stack)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
+          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Dallas, TX</t>
+          <t>Associate, Snowflake Data Engineer – BTO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=440518c253bc8566</t>
+          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer(Strong Testing Experience)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Quadrant Technologies</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>RDS, Google Cloud Platform, HBase, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ae1d7b6ce452d8</t>
+          <t>https://www.indeed.com/viewjob?jk=930af228e501f878</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Data Engineer _ Python with Spark</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8b463a5152c979</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Product Owner II - BI (Memphis, TN or Remote in USA)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea984ba020827de7</t>
+          <t>https://www.indeed.com/viewjob?jk=256f30d9aec8fc7b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Backend Software Engineer III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Assurant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c70bbdfbf97a8c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Azure Data Fabric Engineer</t>
+          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770392</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SLD TECHNOLOGIES LLC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6a7bc10ac96c1a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Popeyes</t>
+          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770393</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Popeyes</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
+          <t>https://www.indeed.com/viewjob?jk=23c054ad41fdd40c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (5+ years)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
+          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ifm efector inc.</t>
+          <t>Main Sail, LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=5675e83788c1c4fd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud &amp; Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>enChoice, Inc.</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Cloud Storage, Scala, Oracle, SQL Server, MongoDB</t>
+          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7de1e2049e683c</t>
+          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software/Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Paradigm Max Q LLC</t>
+          <t>RXO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
+          <t>https://www.indeed.com/viewjob?jk=eedaefa82474ae57</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer- Dallas, TX</t>
+          <t>Performance Test Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,102 +2071,102 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84593a6570df58c9</t>
+          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Software QA Engineer, Logistics</t>
+          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3703a65a658398ce</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Developer (Java Full Stack)</t>
+          <t>Senior Data Engineer - Privacy &amp; Governance</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Data Modeling, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
+          <t>https://www.indeed.com/viewjob?jk=4b85de9f1c3e87c3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer _ Python with Spark</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Rhino</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, ECS, RDS, Scala, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8b463a5152c979</t>
+          <t>https://www.indeed.com/viewjob?jk=42875591a11e5caa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate, Snowflake Data Engineer – BTO</t>
+          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Very LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
+          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
+          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, HBase, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=930af228e501f878</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Urban Dynamics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=256f30d9aec8fc7b</t>
+          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer, MLOps, Manufacturing Quality</t>
+          <t>Software Engineer (Python, Kafka / Confluent)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, ETL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552f3d2b25f75144</t>
+          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Backend ML Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sterling Computers</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>North Sioux City, SD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0c294f11382975</t>
+          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Backend ML Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sterling Computers</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8e8eb0ff879575</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c70bbdfbf97a8c</t>
+          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770392</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6a7bc10ac96c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770393</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c054ad41fdd40c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
+          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Main Sail, LLC</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5675e83788c1c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rhino</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42875591a11e5caa</t>
+          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
+          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a7dc9b2a0c6b63</t>
+          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
+          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RXO</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eedaefa82474ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Performance Test Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
+          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Privacy &amp; Governance</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pacers Sports &amp; Entertainment</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Data Modeling, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b85de9f1c3e87c3</t>
+          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Meridian Cooperative Inc</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad5be160ea34501</t>
+          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Data Architect, Large Scale Distributed Systems</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL, AKS, Git, SQL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab772be531586550</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Urban Dynamics</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
+          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Developer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>voestalpine</t>
+          <t>Synctera</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago Heights, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Manufacturing Systems Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>voestalpine</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
+          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer (Python, Kafka / Confluent)</t>
+          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
+          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL, dbt, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Financial Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>cpg.io eCommerce Distributors</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Addison, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
+          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Data Engineer - Informatica IDMC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
+          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Python Engineer with REST &amp; GenAI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
+          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Backend Engineer — ChainIT Pay</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>ChainIT Pay</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
+          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
+          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Business Intelligence SME – MicroStrategy</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>A1fed</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,15 +3488,15 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,15 +3523,15 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
+          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,15 +3558,15 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
+          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
+          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,15 +3628,15 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
+          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,15 +3663,15 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3698,15 +3698,15 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
+          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,15 +3733,15 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
+          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3768,15 +3768,15 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3803,15 +3803,15 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Synctera</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
+          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer II - Identity &amp; Access Management</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc0ef7396ea02ef</t>
+          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Niagara Bottling</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Diamond Bar, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
+          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL, dbt, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
+          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BlackLine</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48debf03335c270f</t>
+          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Financial Data Engineer</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>cpg.io eCommerce Distributors</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Addison, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
+          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
+          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,847 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=0f93ad8b1a8de327</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Python Engineer with REST &amp; GenAI</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer — ChainIT Pay</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>ChainIT Pay</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Guild Mortgage Company LLC</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Glendale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Business Intelligence SME – MicroStrategy</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>A1fed</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Pelago</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, MySQL, NoSQL</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a095b7520f3a9612</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-13.xlsx
+++ b/results/job_matches_2026-05-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,35 +503,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Supervisor - Cyber Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec208cdfd014f62</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b7c33de4d899ac</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4b12692ab49b7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=aec208cdfd014f62</t>
         </is>
       </c>
     </row>
@@ -578,20 +578,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=569e2680cf991081</t>
+          <t>https://www.indeed.com/viewjob?jk=f4b12692ab49b7bf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Optum Advisory Board - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, S3, Azure, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff403bb7c12a386</t>
+          <t>https://www.indeed.com/viewjob?jk=569e2680cf991081</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer – Baltimore City, MD</t>
+          <t>Data Engineer - Optum Advisory Board - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ac3e71ab2ea33f</t>
+          <t>https://www.indeed.com/viewjob?jk=dff403bb7c12a386</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer – Baltimore City, MD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f200c5b28338d187</t>
+          <t>https://www.indeed.com/viewjob?jk=80ac3e71ab2ea33f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=919dcee2ea81fef5</t>
+          <t>https://www.indeed.com/viewjob?jk=f200c5b28338d187</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4076bfbb84ccf37</t>
+          <t>https://www.indeed.com/viewjob?jk=919dcee2ea81fef5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>#19675 - Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83236b2299aaa9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a4076bfbb84ccf37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - Java</t>
+          <t>#19675 - Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Qualitest</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
+          <t>https://www.indeed.com/viewjob?jk=83236b2299aaa9b3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Specialist</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Creative Realities</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd5bf185da35fd9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Software Engineer - Java</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>POWERX</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d222e67b861731</t>
+          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>DevOps Specialist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Creative Realities</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fuse Fundraising</t>
+          <t>POWERX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
+          <t>https://www.indeed.com/viewjob?jk=78d222e67b861731</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec1df703d4c5e04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer(Strong Testing Experience)</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quadrant Technologies</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ae1d7b6ce452d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Fuse Fundraising</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (5+ years)</t>
+          <t>Sr Databricks Data Engineer(Strong Testing Experience)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Quadrant Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ae1d7b6ce452d8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ifm efector inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Azure Data Fabric Engineer</t>
+          <t>Senior Data Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SLD TECHNOLOGIES LLC</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud &amp; Database Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>enChoice, Inc.</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Cloud Storage, Scala, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7de1e2049e683c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software/Data Engineer</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>ifm efector inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
+          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Azure Data Fabric Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Paradigm Max Q LLC</t>
+          <t>SLD TECHNOLOGIES LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
+          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Cloud &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>enChoice, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Cloud Storage, Scala, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7de1e2049e683c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Senior Software/Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Assurant</t>
+          <t>Paradigm Max Q LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Popeyes</t>
+          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Popeyes</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
+          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Developer (Java Full Stack)</t>
+          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
+          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate, Snowflake Data Engineer – BTO</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Assurant</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr. Software Engineer, Popeyes</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Popeyes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
+          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, HBase, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=930af228e501f878</t>
+          <t>https://www.indeed.com/viewjob?jk=c95e30f564154a4e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer _ Python with Spark</t>
+          <t>Developer (Java Full Stack)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8b463a5152c979</t>
+          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Posture Management Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=256f30d9aec8fc7b</t>
+          <t>https://www.indeed.com/viewjob?jk=eff362c629e77083</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III</t>
+          <t>Associate, Snowflake Data Engineer – BTO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c70bbdfbf97a8c</t>
+          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770392</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6a7bc10ac96c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770393</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, HBase, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c054ad41fdd40c</t>
+          <t>https://www.indeed.com/viewjob?jk=930af228e501f878</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer _ Python with Spark</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8b463a5152c979</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=256f30d9aec8fc7b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Backend Software Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Main Sail, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5675e83788c1c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c70bbdfbf97a8c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770392</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6a7bc10ac96c1a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770393</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
+          <t>https://www.indeed.com/viewjob?jk=23c054ad41fdd40c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RXO</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eedaefa82474ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Performance Test Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
+          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Main Sail, LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=5675e83788c1c4fd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Privacy &amp; Governance</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pacers Sports &amp; Entertainment</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Data Modeling, dbt, Power BI, Tableau, CI/CD</t>
+          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b85de9f1c3e87c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rhino</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42875591a11e5caa</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Very LLC</t>
+          <t>RXO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
+          <t>https://www.indeed.com/viewjob?jk=eedaefa82474ae57</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>Performance Test Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - Privacy &amp; Governance</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Urban Dynamics</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Data Modeling, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
+          <t>https://www.indeed.com/viewjob?jk=4b85de9f1c3e87c3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer (Python, Kafka / Confluent)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Rhino</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Scala, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
+          <t>https://www.indeed.com/viewjob?jk=42875591a11e5caa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
+          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
+          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
+          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
+          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
+          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
+          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
+          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
+          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
+          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
+          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
+          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Synctera</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
+          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Developer</t>
+          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>voestalpine</t>
+          <t>Very LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago Heights, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,42 +3111,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Niagara Bottling</t>
+          <t>Urban Dynamics</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Diamond Bar, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
+          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Software Engineer (Python, Kafka / Confluent)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL, dbt, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
+          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Financial Data Engineer</t>
+          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>cpg.io eCommerce Distributors</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Addison, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
+          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Synctera</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
+          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+          <t>Manufacturing Systems Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>voestalpine</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
+          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Python Engineer with REST &amp; GenAI</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mutual of Enumclaw Insurance</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Enumclaw, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
+          <t>https://www.indeed.com/viewjob?jk=8cfe3ebca43d1190</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer — ChainIT Pay</t>
+          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ChainIT Pay</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
+          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL, dbt, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
+          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Financial Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>cpg.io eCommerce Distributors</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Addison, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
+          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Business Intelligence SME – MicroStrategy</t>
+          <t>Senior Data Engineer - Informatica IDMC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>A1fed</t>
+          <t>SYSTECH USA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
+          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
+          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>AI Data Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, ECS, RDS, Databricks, Spark, Scala, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
+          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Python Engineer with REST &amp; GenAI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
+          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior Backend Engineer — ChainIT Pay</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>ChainIT Pay</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
+          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Business Intelligence SME – MicroStrategy</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>A1fed</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
+          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
+          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
+          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
+          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
+          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
+          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,322 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
+          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
           <t>https://www.indeed.com/viewjob?jk=0f93ad8b1a8de327</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Workday Optimization Consultant</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51eff55258e66e9d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-13.xlsx
+++ b/results/job_matches_2026-05-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=919dcee2ea81fef5</t>
+          <t>https://www.indeed.com/viewjob?jk=6d75dcabdd05e31b</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4076bfbb84ccf37</t>
+          <t>https://www.indeed.com/viewjob?jk=919dcee2ea81fef5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>#19675 - Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,42 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83236b2299aaa9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a4076bfbb84ccf37</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>#19675 - Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualitest</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd5bf185da35fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=83236b2299aaa9b3</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Software Engineerâ€“ Full Stack</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd6f9018a657390</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fuse Fundraising</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Fuse Fundraising</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
+          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer(Strong Testing Experience)</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quadrant Technologies</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ae1d7b6ce452d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Sr Databricks Data Engineer(Strong Testing Experience)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Quadrant Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ae1d7b6ce452d8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
+          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (5+ years)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
+          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ifm efector inc.</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Azure Data Fabric Engineer</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SLD TECHNOLOGIES LLC</t>
+          <t>ifm efector inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
+          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud &amp; Database Engineer</t>
+          <t>Azure Data Fabric Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>enChoice, Inc.</t>
+          <t>SLD TECHNOLOGIES LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Cloud Storage, Scala, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7de1e2049e683c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software/Data Engineer</t>
+          <t>Cloud &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>enChoice, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Cloud Storage, Scala, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7de1e2049e683c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Senior Software/Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Paradigm Max Q LLC</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Paradigm Max Q LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Assurant</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Popeyes</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Popeyes</t>
+          <t>Assurant</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Sr. Software Engineer, Popeyes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Popeyes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95e30f564154a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Developer (Java Full Stack)</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
+          <t>https://www.indeed.com/viewjob?jk=c95e30f564154a4e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Posture Management Engineer</t>
+          <t>​Mobile Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Oracle, NoSQL, Splunk, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff362c629e77083</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d436fc96de41ea</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Associate, Snowflake Data Engineer – BTO</t>
+          <t>Developer (Java Full Stack)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
+          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Associate, Snowflake Data Engineer – BTO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
+          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, HBase, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=930af228e501f878</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Python, CI/CD</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
+          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
+          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RXO</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eedaefa82474ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Performance Test Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>RXO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
+          <t>https://www.indeed.com/viewjob?jk=eedaefa82474ae57</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC &amp; CDGC (Data Lineage &amp; Data Quality)</t>
+          <t>Performance Test Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6fa1054166d69d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rhino</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42875591a11e5caa</t>
+          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Senior Backend Engineer (Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
+          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
+          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
+          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
+          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
+          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
+          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
+          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
+          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
+          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
+          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
+          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
+          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Very LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Very LLC</t>
+          <t>Urban Dynamics</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
+          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer (Python, Kafka / Confluent)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Urban Dynamics</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
+          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer (Python, Kafka / Confluent)</t>
+          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
+          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Synctera</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
+          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Manufacturing Systems Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Synctera</t>
+          <t>voestalpine</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,42 +3261,42 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
+          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Developer</t>
+          <t>Platform Reliability Engineer – Data, Content &amp; Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>voestalpine</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago Heights, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=43204d9b47ac68cd</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Informatica IDMC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SYSTECH USA</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, CI/CD, Git, Python</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfba15617362e81</t>
+          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
+          <t>AWS, ECS, RDS, Databricks, Spark, Scala, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI Data Engineer II</t>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Spark, Scala, ELT, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
+          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Python Engineer with REST &amp; GenAI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Docker, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87e755ed281f268b</t>
+          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+          <t>Senior Backend Engineer — ChainIT Pay</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>ChainIT Pay</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
+          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Python Engineer with REST &amp; GenAI</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
+          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer — ChainIT Pay</t>
+          <t>Business Intelligence SME – MicroStrategy</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ChainIT Pay</t>
+          <t>A1fed</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
+          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Business Intelligence SME – MicroStrategy</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>A1fed</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
+          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
+          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
+          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
+          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
+          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
+          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
+          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
+          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
+          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
+          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
+          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
+          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
+          <t>https://www.indeed.com/viewjob?jk=0f93ad8b1a8de327</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Workday Optimization Consultant</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,85 +4371,15 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f93ad8b1a8de327</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Workday Optimization Consultant</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=51eff55258e66e9d</t>
         </is>

--- a/results/job_matches_2026-05-13.xlsx
+++ b/results/job_matches_2026-05-13.xlsx
@@ -561,12 +561,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec208cdfd014f62</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6324c917198667</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4b12692ab49b7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=aec208cdfd014f62</t>
         </is>
       </c>
     </row>
@@ -613,20 +613,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=569e2680cf991081</t>
+          <t>https://www.indeed.com/viewjob?jk=f4b12692ab49b7bf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Optum Advisory Board - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, S3, Azure, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff403bb7c12a386</t>
+          <t>https://www.indeed.com/viewjob?jk=569e2680cf991081</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f200c5b28338d187</t>
+          <t>https://www.indeed.com/viewjob?jk=6d75dcabdd05e31b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d75dcabdd05e31b</t>
+          <t>https://www.indeed.com/viewjob?jk=919dcee2ea81fef5</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=919dcee2ea81fef5</t>
+          <t>https://www.indeed.com/viewjob?jk=a4076bfbb84ccf37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>#19675 - Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Qualitest</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4076bfbb84ccf37</t>
+          <t>https://www.indeed.com/viewjob?jk=83236b2299aaa9b3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>#19675 - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83236b2299aaa9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer - Java</t>
+          <t>ML (Machine Learning) Engineering Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Step Functions, RDS, Spark, Scala, Kafka, PostgreSQL, ETL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
+          <t>https://www.indeed.com/viewjob?jk=c5732db1baec0796</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Specialist</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Creative Realities</t>
+          <t>POWERX</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
+          <t>https://www.indeed.com/viewjob?jk=78d222e67b861731</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Software Engineer - Java</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>POWERX</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,172 +986,172 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d222e67b861731</t>
+          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>DevOps Specialist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Creative Realities</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec1df703d4c5e04</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineerâ€“ Full Stack</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd6f9018a657390</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec1df703d4c5e04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Senior Software Engineer, MLOps</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Machine Learning, Manufacturing Quality</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fuse Fundraising</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Kafka, Oracle, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af281bb5ea90fb04</t>
+          <t>https://www.indeed.com/viewjob?jk=ae09bf0f698805e7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Software Engineerâ€“ Full Stack</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, S3, Azure, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cd6f9018a657390</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer(Strong Testing Experience)</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quadrant Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ae1d7b6ce452d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8348059168d7d3ed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Select Computing, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,77 +1256,77 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (5+ years)</t>
+          <t>Snowflake Presales Architect (Data &amp; AI)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
+          <t>https://www.indeed.com/viewjob?jk=43b27a2ed9fce658</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Software Engineer- Dallas, TX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ifm efector inc.</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=440518c253bc8566</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure Data Fabric Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SLD TECHNOLOGIES LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
+          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud &amp; Database Engineer</t>
+          <t>Sr Databricks Data Engineer(Strong Testing Experience)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>enChoice, Inc.</t>
+          <t>Quadrant Technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Cloud Storage, Scala, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7de1e2049e683c</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ae1d7b6ce452d8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software/Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, PostgreSQL, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff04daca7022946</t>
+          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Paradigm Max Q LLC</t>
+          <t>CURE Auto Insurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b309f7d0c7f520</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ae9e298623659d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
+          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Senior Data Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Assurant</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Popeyes</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Popeyes</t>
+          <t>ifm efector inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
+          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Azure Data Fabric Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SLD TECHNOLOGIES LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95e30f564154a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>​Mobile Software Engineer</t>
+          <t>Cloud &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>enChoice, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Cloud Storage, Scala, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d436fc96de41ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8f7de1e2049e683c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Developer (Java Full Stack)</t>
+          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
+          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Associate, Snowflake Data Engineer – BTO</t>
+          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
+          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Assurant</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer _ Python with Spark</t>
+          <t>Sr. Software Engineer, Popeyes</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Popeyes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8b463a5152c979</t>
+          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Quality Engineer- Dallas, TX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,137 +1896,137 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=256f30d9aec8fc7b</t>
+          <t>https://www.indeed.com/viewjob?jk=84593a6570df58c9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III</t>
+          <t>MuleSoft Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c70bbdfbf97a8c</t>
+          <t>https://www.indeed.com/viewjob?jk=017b9ce5af5cfa1a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770392</t>
+          <t>Sr. Software QA Engineer, Logistics</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6a7bc10ac96c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=3703a65a658398ce</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770393</t>
+          <t>​Mobile Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c054ad41fdd40c</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d436fc96de41ea</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Developer (Java Full Stack)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
+          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Associate, Snowflake Data Engineer – BTO</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Main Sail, LLC</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5675e83788c1c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Python, CI/CD</t>
+          <t>Senior Data Engineer _ Python with Spark</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8b463a5152c979</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,172 +2176,172 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
+          <t>https://www.indeed.com/viewjob?jk=256f30d9aec8fc7b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>Marks IT Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RXO</t>
+          <t>Revelation Pharma</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eedaefa82474ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=4690228daf5da36a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Performance Test Engineer</t>
+          <t>Software Engineer, MLOps, Manufacturing Quality</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
+          <t>https://www.indeed.com/viewjob?jk=552f3d2b25f75144</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Privacy &amp; Governance</t>
+          <t>Backend ML Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pacers Sports &amp; Entertainment</t>
+          <t>Sterling Computers</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>North Sioux City, SD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Data Modeling, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b85de9f1c3e87c3</t>
+          <t>https://www.indeed.com/viewjob?jk=4d0c294f11382975</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>Backend ML Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Sterling Computers</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8e8eb0ff879575</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Expert Product Architect AI/ML</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=72b34dd2c66213a7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Backend Software Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58554de2ec8995a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c70bbdfbf97a8c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770392</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3f768cf0468176</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6a7bc10ac96c1a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770393</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99a2663edcff3f50</t>
+          <t>https://www.indeed.com/viewjob?jk=23c054ad41fdd40c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbc9cd08b84cd98</t>
+          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0bc38b45daf54f</t>
+          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ce171147829d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Data Engineer - Python, CI/CD</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303dbe21162aedcd</t>
+          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe994dfe0ba2aa27</t>
+          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d761590421f49ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>RXO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892b50984f957507</t>
+          <t>https://www.indeed.com/viewjob?jk=eedaefa82474ae57</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Performance Test Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e8225e252d5b308</t>
+          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Sr. Database Administrator</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Meridian Cooperative Inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410addd619a13132</t>
+          <t>https://www.indeed.com/viewjob?jk=aad5be160ea34501</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Sr. Data Architect, Large Scale Distributed Systems</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL, AKS, Git, SQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d8229a4579bf54</t>
+          <t>https://www.indeed.com/viewjob?jk=ab772be531586550</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Urban Dynamics</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3625b9b2eb13247</t>
+          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, HBase, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e23e0d93a166cf</t>
+          <t>https://www.indeed.com/viewjob?jk=a7337f694f054c6a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Very LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728055e2c8c11c3</t>
+          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c2a11252e4d062</t>
+          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Synctera</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b216e39afb6b76d8</t>
+          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Python) - Content Understanding</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3210e4592c9a0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Very LLC</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Manufacturing Systems Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Urban Dynamics</t>
+          <t>voestalpine</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
+          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
         </is>
       </c>
     </row>
@@ -3163,17 +3163,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Software Engineer II - Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,94 +3191,94 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
+          <t>https://www.indeed.com/viewjob?jk=1bc0ef7396ea02ef</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer – Palantir Foundry</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Synctera</t>
+          <t>objectways</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
+          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Developer</t>
+          <t>Platform Reliability Engineer – Data, Content &amp; Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>voestalpine</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago Heights, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=43204d9b47ac68cd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer – Data, Content &amp; Analytics (Hybrid)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Mutual of Enumclaw Insurance</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Enumclaw, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43204d9b47ac68cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8cfe3ebca43d1190</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Mutual of Enumclaw Insurance</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Enumclaw, WA, US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cfe3ebca43d1190</t>
+          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Niagara Bottling</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Diamond Bar, CA, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL, dbt, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
+          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Senior Financial Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>cpg.io eCommerce Distributors</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Addison, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL, dbt, Git</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
+          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Financial Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>cpg.io eCommerce Distributors</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Addison, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
+          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Oracle Fusion Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
+          <t>RDS, Azure, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
+          <t>https://www.indeed.com/viewjob?jk=091a80e147261d97</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI Data Engineer II</t>
+          <t>Cybersecurity Engineering Associate - .NET</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Spark, Scala, ELT, CI/CD, Terraform, Docker</t>
+          <t>RDS, Scala, SQL Server, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
+          <t>https://www.indeed.com/viewjob?jk=9a52de1f01371097</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+          <t>Cybersecurity Engineering Associate - .NET</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Scala, SQL Server, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
+          <t>https://www.indeed.com/viewjob?jk=22813c7deaeeb0b9</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Python Engineer with REST &amp; GenAI</t>
+          <t>Cybersecurity Engineering Associate - .NET</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, SQL Server, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
+          <t>https://www.indeed.com/viewjob?jk=185fbf34ac3ae2ea</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer — ChainIT Pay</t>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ChainIT Pay</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, RDS, Azure, YARN, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632c5a674bd9833e</t>
+          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Data Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, DataOps, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Databricks, Spark, Scala, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d656dac9920b857b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
         </is>
       </c>
     </row>
@@ -4353,17 +4353,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Workday Optimization Consultant</t>
+          <t>Python Engineer with REST &amp; GenAI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,17 +4371,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51eff55258e66e9d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-13.xlsx
+++ b/results/job_matches_2026-05-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Supervisor - Cyber Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b7c33de4d899ac</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6324c917198667</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6324c917198667</t>
+          <t>https://www.indeed.com/viewjob?jk=aec208cdfd014f62</t>
         </is>
       </c>
     </row>
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec208cdfd014f62</t>
+          <t>https://www.indeed.com/viewjob?jk=f4b12692ab49b7bf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer – Baltimore City, MD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4b12692ab49b7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=80ac3e71ab2ea33f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>0000001423.AI ENGINEER II.INFO TECH - DATA AND AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume, Spark</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=569e2680cf991081</t>
+          <t>https://www.indeed.com/viewjob?jk=8e292fecba5a3f54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer – Baltimore City, MD</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ac3e71ab2ea33f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d75dcabdd05e31b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DELVIX EDGE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d75dcabdd05e31b</t>
+          <t>https://www.indeed.com/viewjob?jk=3059a32608f8fae5</t>
         </is>
       </c>
     </row>
@@ -818,87 +818,87 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>#19675 - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83236b2299aaa9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Java</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
+          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ML (Machine Learning) Engineering Consultant</t>
+          <t>DevOps Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Creative Realities</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Spark, Scala, Kafka, PostgreSQL, ETL, MLOps, MLflow</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5732db1baec0796</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
         </is>
       </c>
     </row>
@@ -958,87 +958,87 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer - Java</t>
+          <t>Senior Software Engineer (Data Engineering)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
+          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Specialist</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Creative Realities</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec1df703d4c5e04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Software Engineer, MLOps</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,77 +1046,77 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec1df703d4c5e04</t>
+          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, MLOps</t>
+          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Premier Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
+          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer, Machine Learning, Manufacturing Quality</t>
+          <t>Application Developer - ETL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Kafka, Oracle, MySQL, MongoDB</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae09bf0f698805e7</t>
+          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineerâ€“ Full Stack</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cd6f9018a657390</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Select Computing, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8348059168d7d3ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Select Computing, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,77 +1256,77 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Snowflake Presales Architect (Data &amp; AI)</t>
+          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43b27a2ed9fce658</t>
+          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
+          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Dallas, TX</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Assurant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=440518c253bc8566</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data Fabric Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SLD TECHNOLOGIES LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
+          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Databricks Data Engineer(Strong Testing Experience)</t>
+          <t>Sr. Software Engineer, Popeyes</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Quadrant Technologies</t>
+          <t>Popeyes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,94 +1441,94 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ae1d7b6ce452d8</t>
+          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d799dce46a222f6f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CURE Auto Insurance</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
+          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ae9e298623659d</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (5+ years)</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>ifm efector inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
+          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>​Mobile Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d436fc96de41ea</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ifm efector inc.</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure Data Fabric Engineer</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SLD TECHNOLOGIES LLC</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
+          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud &amp; Database Engineer</t>
+          <t>Senior Data Engineer _ Python with Spark</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>enChoice, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Cloud Storage, Scala, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f7de1e2049e683c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8b463a5152c979</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Associate, Snowflake Data Engineer – BTO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
+          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Assurant</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, HBase, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=930af228e501f878</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Popeyes</t>
+          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Popeyes</t>
+          <t>Marks IT Solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer- Dallas, TX</t>
+          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770392</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,137 +1896,137 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84593a6570df58c9</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6a7bc10ac96c1a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MuleSoft Architect</t>
+          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770393</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=017b9ce5af5cfa1a</t>
+          <t>https://www.indeed.com/viewjob?jk=23c054ad41fdd40c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software QA Engineer, Logistics</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3703a65a658398ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>​Mobile Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d436fc96de41ea</t>
+          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Developer (Java Full Stack)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Watts Water Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,137 +2036,137 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=441150d8faf9caf5</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate, Snowflake Data Engineer – BTO</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
+          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
+          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer _ Python with Spark</t>
+          <t>Senior Data Engineer - Python, CI/CD</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8b463a5152c979</t>
+          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Databricks Lakehouse, Data Modeling</t>
+          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,102 +2176,102 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=256f30d9aec8fc7b</t>
+          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Marks IT Solutions</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4690228daf5da36a</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer, MLOps, Manufacturing Quality</t>
+          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Very LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, MongoDB, NoSQL, ETL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552f3d2b25f75144</t>
+          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Backend ML Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sterling Computers</t>
+          <t>Urban Dynamics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>North Sioux City, SD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d0c294f11382975</t>
+          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Backend ML Engineer</t>
+          <t>Software Engineer (Python, Kafka / Confluent)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sterling Computers</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8e8eb0ff879575</t>
+          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Expert Product Architect AI/ML</t>
+          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, Terraform</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b34dd2c66213a7</t>
+          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Synctera</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c70bbdfbf97a8c</t>
+          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770392</t>
+          <t>Manufacturing Systems Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>voestalpine</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,102 +2456,102 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6a7bc10ac96c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770393</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c054ad41fdd40c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
+          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,172 +2561,172 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
+          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Python, CI/CD</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL, dbt, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
+          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Palantir Foundry</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>objectways</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
+          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Reliability Engineer – Data, Content &amp; Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
+          <t>https://www.indeed.com/viewjob?jk=43204d9b47ac68cd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RXO</t>
+          <t>Mutual of Enumclaw Insurance</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Enumclaw, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eedaefa82474ae57</t>
+          <t>https://www.indeed.com/viewjob?jk=8cfe3ebca43d1190</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Performance Test Engineer</t>
+          <t>Senior Financial Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>cpg.io eCommerce Distributors</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Addison, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Scala, Oracle, Splunk</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e993be5e41a8574</t>
+          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Database Administrator</t>
+          <t>AI Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Meridian Cooperative Inc</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, ECS, RDS, Databricks, Spark, Scala, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad5be160ea34501</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Data Architect, Large Scale Distributed Systems</t>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL, AKS, Git, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab772be531586550</t>
+          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python Engineer with REST &amp; GenAI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Urban Dynamics</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Business Intelligence SME – MicroStrategy</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>A1fed</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, PostgreSQL, MongoDB, Cassandra, NoSQL, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7337f694f054c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Very LLC</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
+          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Synctera</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
+          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Developer</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>voestalpine</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago Heights, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer (Python, Kafka / Confluent)</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
+          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer II - Identity &amp; Access Management</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc0ef7396ea02ef</t>
+          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Palantir Foundry</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>objectways</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
+          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer – Data, Content &amp; Analytics (Hybrid)</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43204d9b47ac68cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mutual of Enumclaw Insurance</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Enumclaw, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cfe3ebca43d1190</t>
+          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Niagara Bottling</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Diamond Bar, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
+          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL, dbt, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Financial Data Engineer</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>cpg.io eCommerce Distributors</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Addison, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
+          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Oracle Fusion Architect</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=091a80e147261d97</t>
+          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineering Associate - .NET</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a52de1f01371097</t>
+          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineering Associate - .NET</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22813c7deaeeb0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineering Associate - .NET</t>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,822 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MongoDB, NoSQL, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185fbf34ac3ae2ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>AI Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>EchoStar</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Databricks, Spark, Scala, ELT, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Business Intelligence SME – MicroStrategy</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>A1fed</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=0f93ad8b1a8de327</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Python Engineer with REST &amp; GenAI</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-13.xlsx
+++ b/results/job_matches_2026-05-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,20 +823,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Bridgeway Benefit Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Maple Shade, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,199 +846,199 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
+          <t>https://www.indeed.com/viewjob?jk=93da204448eced35</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Specialist</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Creative Realities</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>POWERX</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d222e67b861731</t>
+          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering)</t>
+          <t>Software Engineer - Java</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
+          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>DevOps Specialist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Creative Realities</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec1df703d4c5e04</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, MLOps</t>
+          <t>Sr. Data Engineer, Enterprise - Slack</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,77 +1046,77 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, EMR, S3, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
+          <t>https://www.indeed.com/viewjob?jk=4d23fbcc1f6757ba</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
+          <t>Senior Software Engineer (Data Engineering)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Premier Health</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
+          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Application Developer - ETL</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec1df703d4c5e04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Senior Software Engineer, MLOps</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Select Computing, Inc.</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
+          <t>AWS, S3, SNS, IAM, RDS, Spark, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,137 +1196,137 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb3e6d3ac433b29</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Application Developer - ETL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
+          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Premier Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
+          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>SR. Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>United Utility</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
+          <t>https://www.indeed.com/viewjob?jk=5e293829bcd26a4c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,172 +1336,172 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Assurant</t>
+          <t>Select Computing, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure Data Fabric Engineer</t>
+          <t>AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SLD TECHNOLOGIES LLC</t>
+          <t>Wiss &amp; Company, LLP</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, ETL, dbt, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0eec70b87f9858</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Popeyes</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Popeyes</t>
+          <t>Upwave</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, Kinesis, S3, Scala, MySQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06d9d4b732d1aa48</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8a2c5811cb8da3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (5+ years)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
+          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Data Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ifm efector inc.</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>​Mobile Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d436fc96de41ea</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
+          <t>Data Warehouse Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>ifm efector inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
+          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
+          <t>Azure Data Fabric Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>SLD TECHNOLOGIES LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer _ Python with Spark</t>
+          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c8b463a5152c979</t>
+          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Associate, Snowflake Data Engineer – BTO</t>
+          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
+          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Assurant</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, HBase, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=930af228e501f878</t>
+          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
+          <t>​Mobile Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Marks IT Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,94 +1861,94 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d436fc96de41ea</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770392</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6a7bc10ac96c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PEGA - Sr Full Stack Engineer with AI/LLM Integrations - 00068770393</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c054ad41fdd40c</t>
+          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef992c4b82254a86</t>
+          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Associate, Snowflake Data Engineer – BTO</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fdee09cb474dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Watts Water Technologies</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f8e75c6761842</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>RDS, Google Cloud Platform, HBase, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
+          <t>https://www.indeed.com/viewjob?jk=930af228e501f878</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Marks IT Solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Python, CI/CD</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Industrial Electric Manufacturing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
+          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
         </is>
       </c>
     </row>
@@ -2153,12 +2153,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
+          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Senior Data Engineer - Python, CI/CD</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Very LLC</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
+          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Urban Dynamics</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer (Python, Kafka / Confluent)</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Very LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,29 +2376,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
+          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Synctera</t>
+          <t>Urban Dynamics</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Snowflake, PostgreSQL, dbt, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de5f0f370de70f71</t>
+          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Developer</t>
+          <t>Software Engineer (Python, Kafka / Confluent)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>voestalpine</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago Heights, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2477,73 +2477,73 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
+          <t>Manufacturing Systems Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>voestalpine</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Chicago Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
+          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
+          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
+          <t>Senior Data Engineer – Palantir Foundry</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Niagara Bottling</t>
+          <t>objectways</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Diamond Bar, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
+          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Platform Reliability Engineer – Data, Content &amp; Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL, dbt, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
+          <t>https://www.indeed.com/viewjob?jk=43204d9b47ac68cd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Palantir Foundry</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>objectways</t>
+          <t>Mutual of Enumclaw Insurance</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Enumclaw, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
+          <t>https://www.indeed.com/viewjob?jk=8cfe3ebca43d1190</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer – Data, Content &amp; Analytics (Hybrid)</t>
+          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43204d9b47ac68cd</t>
+          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mutual of Enumclaw Insurance</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Enumclaw, WA, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL, dbt, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cfe3ebca43d1190</t>
+          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Financial Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>cpg.io eCommerce Distributors</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Addison, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84dfece3c2e1aec</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Spark, Scala, ELT, CI/CD, Terraform, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
+          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+          <t>Data Engineer, People Innovation Labs</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
+          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Python Engineer with REST &amp; GenAI</t>
+          <t>AI Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Databricks, Spark, Scala, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business Intelligence SME – MicroStrategy</t>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A1fed</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
+          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Python Engineer with REST &amp; GenAI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
+          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Business Intelligence SME – MicroStrategy</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>A1fed</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
+          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
+          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
+          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
+          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
+          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
+          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
+          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
+          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
+          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3575,6 +3575,76 @@
         </is>
       </c>
       <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0f93ad8b1a8de327</t>
         </is>

--- a/results/job_matches_2026-05-13.xlsx
+++ b/results/job_matches_2026-05-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Engineer, Ent Arch</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>9amHealth</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, IAM, RDS, Azure, Cloud Storage, Snowflake</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618fbf33fe541db8</t>
+          <t>https://www.indeed.com/viewjob?jk=204b0fbde6acaec8</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer – Baltimore City, MD</t>
+          <t>Software Engineer, Sr. Consultant - Fullstack GenAI Enablement</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80ac3e71ab2ea33f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c9240c1f60b916</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>CMT Services INC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=919dcee2ea81fef5</t>
+          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4076bfbb84ccf37</t>
+          <t>https://www.indeed.com/viewjob?jk=25ad143bf215dca2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bridgeway Benefit Technologies</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Maple Shade, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,77 +836,77 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93da204448eced35</t>
+          <t>https://www.indeed.com/viewjob?jk=919dcee2ea81fef5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
+          <t>https://www.indeed.com/viewjob?jk=a4076bfbb84ccf37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Bridgeway Benefit Technologies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Maple Shade, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
+          <t>Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
+          <t>https://www.indeed.com/viewjob?jk=93da204448eced35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
+          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer - Java</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Specialist</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Creative Realities</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise - Slack</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d23fbcc1f6757ba</t>
+          <t>https://www.indeed.com/viewjob?jk=380cf25a1caed88b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering)</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e9d4486acb8678</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec1df703d4c5e04</t>
+          <t>https://www.indeed.com/viewjob?jk=37bbb011f9ed9bce</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, MLOps</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
+          <t>https://www.indeed.com/viewjob?jk=cbab770adbb8a52e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, IAM, RDS, Spark, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb3e6d3ac433b29</t>
+          <t>https://www.indeed.com/viewjob?jk=a0eeb94a75d20a86</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Application Developer - ETL</t>
+          <t>Software Engineer - Java</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
+          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
+          <t>DevOps Specialist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Premier Health</t>
+          <t>Creative Realities</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SR. Data Architect</t>
+          <t>Data Scientist / Software Engineer - REMOTE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>United Utility</t>
+          <t>Binary Defense</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, Azure, GCP, Vertex AI, Hadoop, Spark, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e293829bcd26a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Sr. Data Engineer, Enterprise - Slack</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,46 +1322,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, EMR, S3, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d23fbcc1f6757ba</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
+          <t>Senior Software Engineer (Data Engineering)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Select Computing, Inc.</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wiss &amp; Company, LLP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Florham Park, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, ETL, dbt, MLOps</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,242 +1406,242 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0eec70b87f9858</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec1df703d4c5e04</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, MLOps</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Upwave</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, S3, Scala, MySQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8a2c5811cb8da3</t>
+          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Premier Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
+          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Developer - ETL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de13e412e9eb12ce</t>
+          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (5+ years)</t>
+          <t>Jr. Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Kimball, Snowflake Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
+          <t>https://www.indeed.com/viewjob?jk=74de48d3af0aad60</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Select Computing, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Warehouse Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ifm efector inc.</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c320ee229f995ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure Data Fabric Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SLD TECHNOLOGIES LLC</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb01ba3a845df915</t>
+          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
+          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>​Mobile Software Engineer</t>
+          <t>Senior Data Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d436fc96de41ea</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
+          <t>Senior Solutions Architect - HR Technology</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Engineer IV</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,129 +1966,129 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Associate, Snowflake Data Engineer – BTO</t>
+          <t>​Mobile Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d436fc96de41ea</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
+          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, HBase, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=930af228e501f878</t>
+          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Marks IT Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,137 +2106,137 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Associate, Snowflake Data Engineer – BTO</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Industrial Electric Manufacturing</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
+          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Google Cloud Platform, HBase, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
+          <t>https://www.indeed.com/viewjob?jk=930af228e501f878</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Python, CI/CD</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
+          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2267,116 +2267,116 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
+          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Very LLC</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,172 +2386,172 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
+          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Urban Dynamics</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=775f202a52a009bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer (Python, Kafka / Confluent)</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b144ea348f35fc</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Developer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>voestalpine</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago Heights, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
+          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Palantir Foundry</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>objectways</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
+          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer – Data, Content &amp; Analytics (Hybrid)</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,137 +2631,137 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43204d9b47ac68cd</t>
+          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mutual of Enumclaw Insurance</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Enumclaw, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cfe3ebca43d1190</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Niagara Bottling</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Diamond Bar, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
+          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>National Basketball Association</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL, dbt, Git</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e327a1ee260319b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
+          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer, People Innovation Labs</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,312 +2841,312 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
+          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Data Engineer II</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Spark, Scala, ELT, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>University of Miami</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
+          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Python Engineer with REST &amp; GenAI</t>
+          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Marks IT Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3132514d774e51d</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Business Intelligence SME – MicroStrategy</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A1fed</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Industrial Electric Manufacturing</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
+          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
+          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
+          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior Data Engineer - Python, CI/CD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
+          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
+          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Very LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
+          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
+          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Augeo Affinity Marketing, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
+          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Manufacturing Systems Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>voestalpine</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
+          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
+          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
+          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior Data Engineer – Palantir Foundry</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>objectways</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
+          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Platform Reliability Engineer – Data, Content &amp; Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
+          <t>https://www.indeed.com/viewjob?jk=43204d9b47ac68cd</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Mutual of Enumclaw Insurance</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Enumclaw, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=8cfe3ebca43d1190</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Paramount Global US Inc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,15 +3636,960 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>AWS, Hadoop, HDFS, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=741583eb645f2b61</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AI Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>EchoStar</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Databricks, Spark, Scala, ELT, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Reporting Engineer - Hybrid / Remote</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Surgery Partners</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Data Engineer, People Innovation Labs</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SQL/Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b078bd21fd98c8d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full stack (Angular/Java) (Remote)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Cloud Storage, Scala, MySQL, ETL, GitHub Actions, Docker, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7acce88de00e812</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Business Intelligence SME – MicroStrategy</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>A1fed</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0f93ad8b1a8de327</t>
         </is>

--- a/results/job_matches_2026-05-13.xlsx
+++ b/results/job_matches_2026-05-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer - Cloud Applications</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d75dcabdd05e31b</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc7cb699ca48c49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Cloud Applications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DELVIX EDGE</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3059a32608f8fae5</t>
+          <t>https://www.indeed.com/viewjob?jk=25dd86b5d7c3e977</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CMT Services INC</t>
+          <t>DELVIX EDGE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
+          <t>https://www.indeed.com/viewjob?jk=3059a32608f8fae5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid / Remote</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>CMT Services INC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ad143bf215dca2</t>
+          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=919dcee2ea81fef5</t>
+          <t>https://www.indeed.com/viewjob?jk=25ad143bf215dca2</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4076bfbb84ccf37</t>
+          <t>https://www.indeed.com/viewjob?jk=919dcee2ea81fef5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bridgeway Benefit Technologies</t>
+          <t>Stifel</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Maple Shade, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93da204448eced35</t>
+          <t>https://www.indeed.com/viewjob?jk=a4076bfbb84ccf37</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. APIM Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
+          <t>https://www.indeed.com/viewjob?jk=254d152353d4fb63</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Bridgeway Benefit Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Maple Shade, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
+          <t>Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
+          <t>https://www.indeed.com/viewjob?jk=93da204448eced35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
+          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Senior Software Engineer, Backend Services</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=380cf25a1caed88b</t>
+          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e9d4486acb8678</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bbb011f9ed9bce</t>
+          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Software Engineer - Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbab770adbb8a52e</t>
+          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0eeb94a75d20a86</t>
+          <t>https://www.indeed.com/viewjob?jk=380cf25a1caed88b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer - Java</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242f984a6124a7d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e9d4486acb8678</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Specialist</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Creative Realities</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
+          <t>https://www.indeed.com/viewjob?jk=37bbb011f9ed9bce</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist / Software Engineer - REMOTE</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Binary Defense</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Vertex AI, Hadoop, Spark, NoSQL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=cbab770adbb8a52e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise - Slack</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d23fbcc1f6757ba</t>
+          <t>https://www.indeed.com/viewjob?jk=a0eeb94a75d20a86</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering)</t>
+          <t>DevOps Specialist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Creative Realities</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a90989e0e0443f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Scientist / Software Engineer - REMOTE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Binary Defense</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, ECS, Azure, GCP, Vertex AI, Hadoop, Spark, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec1df703d4c5e04</t>
+          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, MLOps</t>
+          <t>Sr. Data Engineer, Enterprise - Slack</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,77 +1431,77 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, EMR, S3, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
+          <t>https://www.indeed.com/viewjob?jk=4d23fbcc1f6757ba</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
+          <t>Senior Software Engineer (Data Engineering)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Premier Health</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
+          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Application Developer - ETL</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,102 +1511,102 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec1df703d4c5e04</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Senior Software Engineer, MLOps</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jr. Data Engineer</t>
+          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Premier Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Kimball, Snowflake Schema, Dimension Tables</t>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74de48d3af0aad60</t>
+          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
+          <t>Application Developer - ETL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Select Computing, Inc.</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,172 +1616,172 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Java AWS Developer Payments</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
+          <t>https://www.indeed.com/viewjob?jk=e3b8be749b58fda2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Jr. Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Kimball, Snowflake Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
+          <t>https://www.indeed.com/viewjob?jk=74de48d3af0aad60</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Select Computing, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Assurant</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
+          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (5+ years)</t>
+          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
+          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - HR Technology</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Assurant</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
+          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>​Mobile Software Engineer</t>
+          <t>Senior Data Engineer (5+ years)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Foresite Labs</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9d436fc96de41ea</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>Outlook Amusements</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>La Crescenta, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
+          <t>Majesco Migration - Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=8eef2c3133811ae9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Engineer IV</t>
+          <t>Senior Solutions Architect - HR Technology</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,137 +2106,137 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate, Snowflake Data Engineer – BTO</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>​Mobile Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28b680ea7e98de</t>
+          <t>https://www.indeed.com/viewjob?jk=e9d436fc96de41ea</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, HBase, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=930af228e501f878</t>
+          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
+          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
+          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Associate, Snowflake Data Engineer – BTO</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
+          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Technical Architect (BIBA)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0ada48dbcb0fb083</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
+          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
+          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
+          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
+          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
+          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
+          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
+          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>University of Miami</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Marks IT Solutions</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Industrial Electric Manufacturing</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>University of Miami</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
+          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Marks IT Solutions</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Python, CI/CD</t>
+          <t>Data Engineer (AWS Redshift/Python)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
+          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
+          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Industrial Electric Manufacturing</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Very LLC</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
+          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Agent Platform</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Snowflake, PostgreSQL, Cassandra, NoSQL, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295e6777ea02d3a2</t>
+          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Data Engineer - Python, CI/CD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Augeo Affinity Marketing, Inc.</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
+          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>voestalpine</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago Heights, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=6715e4c4956d2eae</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
+          <t>AI Application Developer III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
+          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Application Developer III -Houston, TX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,67 +3471,67 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
+          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
+          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Niagara Bottling</t>
+          <t>Very LLC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Diamond Bar, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
+          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Palantir Foundry</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>objectways</t>
+          <t>Augeo Affinity Marketing, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,59 +3541,59 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
+          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer – Data, Content &amp; Analytics (Hybrid)</t>
+          <t>Manufacturing Systems Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>voestalpine</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chicago Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43204d9b47ac68cd</t>
+          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mutual of Enumclaw Insurance</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Enumclaw, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
+          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cfe3ebca43d1190</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Paramount Global US Inc</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741583eb645f2b61</t>
+          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Spark, Scala, ELT, CI/CD, Terraform, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
+          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
+          <t>Enterprise Data Foundation &amp; Intelligent Automation Engineer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
+          <t>https://www.indeed.com/viewjob?jk=601ef9d154530877</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer, People Innovation Labs</t>
+          <t>Senior Data Engineer – Palantir Foundry</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>objectways</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
+          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
+          <t>Platform Reliability Engineer – Data, Content &amp; Analytics (Hybrid)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
+          <t>https://www.indeed.com/viewjob?jk=43204d9b47ac68cd</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Mutual of Enumclaw Insurance</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Enumclaw, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
+          <t>https://www.indeed.com/viewjob?jk=8cfe3ebca43d1190</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SQL/Power BI Developer</t>
+          <t>TypeScript Backend Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Kafka, DynamoDB, NoSQL, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b078bd21fd98c8d7</t>
+          <t>https://www.indeed.com/viewjob?jk=806e6d1aea5231f7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full stack (Angular/Java) (Remote)</t>
+          <t>V&amp;V Engineer – AI - Driven Testing &amp; Validation</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Cloud Storage, Scala, MySQL, ETL, GitHub Actions, Docker, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7acce88de00e812</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e47c4f9f9521bc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Business Intelligence SME – MicroStrategy</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>A1fed</t>
+          <t>Paramount Global US Inc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
+          <t>AWS, Hadoop, HDFS, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
+          <t>https://www.indeed.com/viewjob?jk=741583eb645f2b61</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>AI Data Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, ECS, RDS, Databricks, Spark, Scala, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
+          <t>https://www.indeed.com/viewjob?jk=1d7f0cb7dd1cecd1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
+          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Data Engineer, People Innovation Labs</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
+          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior System Software Engineer - DevOps and Infrastructure Automation</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
+          <t>https://www.indeed.com/viewjob?jk=53035edad0202e59</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>SQL/Power BI Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
+          <t>https://www.indeed.com/viewjob?jk=b078bd21fd98c8d7</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Senior Software Engineer - Full stack (Angular/Java) (Remote)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>RDS, BigQuery, Cloud Storage, Scala, MySQL, ETL, GitHub Actions, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7acce88de00e812</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+          <t>Business Intelligence SME – MicroStrategy</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>A1fed</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
+          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
+          <t>https://www.indeed.com/viewjob?jk=a41e33720748eba0</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
+          <t>https://www.indeed.com/viewjob?jk=66e25691f37ba504</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=03c59d94b34e2f80</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d634bbad366fe2d9</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
+          <t>https://www.indeed.com/viewjob?jk=a95d5752a8ed365a</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa2072bb9699937</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
+          <t>https://www.indeed.com/viewjob?jk=34eb7707f1540ab2</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
+          <t>https://www.indeed.com/viewjob?jk=66c1c677b88a3012</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
+          <t>https://www.indeed.com/viewjob?jk=9980c298fd574440</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbfcb10d4bfdb6</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4590,6 +4590,286 @@
         </is>
       </c>
       <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d91b4eab129a9ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a39b9f4652ab55f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a83f7bb319e75be</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da0c4d8484ccceb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8a87068f87af733</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=686f38dfd1f722de</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f11e909b391eb505</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b786a24cc414ec3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer (Ruby on Rails/Python) - Content Foundations</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0f93ad8b1a8de327</t>
         </is>
